--- a/dataset/3_tax_and_charges_rules/structured/Income_tax_rules_by_year.xlsx
+++ b/dataset/3_tax_and_charges_rules/structured/Income_tax_rules_by_year.xlsx
@@ -26,19 +26,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-  </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -54,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -62,31 +51,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -385,65 +355,178 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>turnover_limit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>fee</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>40269</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2012-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>6000000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S71 Finance Bill 2010 memorandum: the limit for business goes from forty lakh to sixty lakh rupees, effective assessment year 2011-12, i.e. financial year 2010-11; fee S78</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>turnover_limit is from the source (primary). fee is assumed: no law or ICAI scale fixes it. F&amp;O specialist firms quote Rs 14,000 for audit, accounts and return together, and a general fee guide puts audits of Rs 1 crore to 5 crore of turnover at Rs 25,000 to 60,000 and below Rs 1 crore at Rs 10,000 to 25,000 (S78); Rs 25,000 is where those ranges meet. One nominal figure is used for every year, taken as all-in (GST included) and deducted as a business cost. Asking prices of 2026, not the fees of the year.</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>41000</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>10000000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S72 Finance Bill 2012 memorandum: the limit for business goes from sixty lakh to one crore rupees, effective assessment year 2013-14, i.e. financial year 2012-13; fee S78</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>turnover_limit is from the source (primary). fee is assumed, as in the first row: Rs 25,000, all-in, one nominal figure for every year (S78).</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>43556</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>50000000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S73 Finance Bill 2020 memorandum: one crore becomes five crore rupees where cash receipts and cash payments are each at most five per cent, effective assessment year 2020-21, i.e. financial year 2019-20; fee S78</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>turnover_limit is from the source (primary) and assumes the two cash tests are met (see the top of this file); without them it is Rs 1 crore. fee is assumed: Rs 25,000, all-in (S78).</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>43922</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -460,8 +543,10 @@
           <t>S74 Finance Bill 2021 memorandum: five crore becomes ten crore rupees on the same two cash tests, effective assessment year 2021-22, i.e. financial year 2020-21; S76 Income-tax Act 2025 section 63(1) keeps one crore and ten crore from 2026-04-01; fee S78</t>
         </is>
       </c>
-      <c r="F5" s="2">
-        <v>46295</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -485,62 +570,62 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>income_limit</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>max_rebate</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>applies_to_special</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>marginal_relief</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>excluded_sections</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -552,6 +637,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2013-03-31</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>S19 Finance Bill 2013 memorandum: the rebate of Rs 2000 is new, from AY 2014-15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No rebate for individuals in financial years 2010-11 to 2012-13.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -559,6 +695,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>S19 Finance Bill 2013 memorandum: rebate equal to the tax or Rs 2000, whichever is less, for a resident individual with total income up to Rs 5 lakh, from AY 2014-15; S59 confirms the existing Rs 2000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Financial years 2013-14 to 2015-16. Taken from the tax on total income, including tax on short-term equity gains (section 87A has no exclusion for them, S68).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -566,6 +753,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>S59 Finance Bill 2016 memorandum: rebate raised from Rs 2,000 to Rs 5,000 from AY 2017-18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Financial year 2016-17.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -573,6 +811,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>S44 Finance Bill 2017 memorandum: rebate cut to Rs 2500 for total income up to Rs 3,50,000, from AY 2018-19</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Financial year 2017-18.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -580,6 +869,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>350000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>["112A"]</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>S44 Rs 2500 up to Rs 3.5 lakh continues (S60 changes it only from 2020-04-01); S68 section 112A(6): the rebate is taken from the tax on total income reduced by the tax on section 112A gains</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Financial year 2018-19. Section 112A exists from this year.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -587,6 +927,57 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>["112A"]</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>S60 Finance Bill 2019 clause 8: rebate Rs 12,500 for total income up to Rs 5,00,000 from AY 2020-21; S64 and S65 confirm Rs 5 lakh in 2023-24 to 2025-26; S68 section 112A(6)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Financial years 2019-20 to 2025-26. No marginal relief in this regime: one rupee over Rs 5 lakh loses the whole rebate.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -594,6 +985,52 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>["198 (2025 Act)"]</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>S70 Income-tax Act 2025 section 156(1): 100% of the tax or Rs 12,500 for total income up to Rs 5,00,000; S55 section 198 is the successor of section 112A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Financial year 2026-27 (tax year 2026-27).</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -601,6 +1038,57 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>500000</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>12500</t>
+        </is>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>["112A"]</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>S64 Finance Bill 2023 memorandum: a resident individual with total income up to Rs 5 lakh gets a rebate of the whole tax (Rs 12,500 at most, S60); the new regime had no exclusion before 2023-24</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Financial years 2020-21 to 2022-23: the same rebate as the old regime.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,6 +1096,57 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>700000</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>S64 rebate up to Rs 25,000 for total income up to Rs 7 lakh under section 115BAC(1A) from AY 2024-25, marginal relief above; S65 para 3: tax on income at special rates is not included in the rebate</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>The limits are from the law. The special-rate part is ASSUMED: the department's stated reading (S65) is that the rebate does not cover tax on section 111A and 112 gains, and its processing denied it, but ITAT Ahmedabad (S68, 12 Aug 2025) allowed it against section 111A tax for AY 2024-25. The department's reading is used, which gives the higher tax.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -636,16 +1175,20 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="G11" s="2">
-        <v>45748</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>S65 Finance Bill 2025 memorandum para 4 and 5: from AY 2026-27 rebate Rs 60,000 for total income up to Rs 12 lakh, with marginal relief, not available on tax on income at special rates; S70 section 156(2) and (3)</t>
         </is>
       </c>
-      <c r="J11" s="2">
-        <v>46295</v>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -669,42 +1212,42 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>brackets</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -716,6 +1259,36 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[{"upto": "160000", "rate": "0"}, {"upto": "500000", "rate": "0.10"}, {"upto": "800000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2011-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S56 Finance Bill 2010 memorandum: Upto Rs. 1,60,000 Nil; to Rs. 5,00,000 10 per cent; to Rs. 8,00,000 20 per cent; above 30 per cent</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -723,6 +1296,36 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[{"upto": "180000", "rate": "0"}, {"upto": "500000", "rate": "0.10"}, {"upto": "800000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2012-03-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S57 Finance Bill 2011 memorandum: Upto Rs. 1,80,000 Nil; to Rs. 5,00,000 10 per cent; to Rs. 8,00,000 20 per cent; above 30 per cent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -730,6 +1333,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[{"upto": "200000", "rate": "0"}, {"upto": "500000", "rate": "0.10"}, {"upto": "1000000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S40 Finance Bill 2012 memorandum: Upto Rs. 2,00,000 Nil; to Rs. 5,00,000 10 per cent; to Rs. 10,00,000 20 per cent; above 30 per cent; S19 the 2013 Bill keeps the same rates</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Financial years 2012-13 and 2013-14.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -737,6 +1375,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[{"upto": "250000", "rate": "0"}, {"upto": "500000", "rate": "0.10"}, {"upto": "1000000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S41 Finance Bill 2014 memorandum: Upto Rs. 2,50,000 Nil; to Rs. 5,00,000 10 per cent; to Rs. 10,00,000 20 per cent; above 30 per cent; S58 and S59 the 2015 and 2016 Bills keep them</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Financial years 2014-15, 2015-16 and 2016-17.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,6 +1417,36 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[{"upto": "250000", "rate": "0"}, {"upto": "500000", "rate": "0.05"}, {"upto": "1000000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S44 Finance Bill 2017 memorandum: Rs. 2,50,001 to Rs. 5,00,000 5 per cent; to Rs. 10,00,000 20 per cent; above 30 per cent; S43, S61, S45, S62, S63, S64, S47, S65 and S55 (Finance Bill 2026, old-regime option) show the same slabs in later years</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Financial years 2017-18 onward. Unchanged in every later Finance Act; for 2026-27 it is the option under section 202(4) of the Income-tax Act 2025.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -751,6 +1454,41 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[{"upto": "250000", "rate": "0"}, {"upto": "500000", "rate": "0.05"}, {"upto": "750000", "rate": "0.10"}, {"upto": "1000000", "rate": "0.15"}, {"upto": "1250000", "rate": "0.20"}, {"upto": "1500000", "rate": "0.25"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S45 Finance Bill 2020 memorandum, section 115BAC: to Rs 2,50,000 Nil; 5 per cent to 5,00,000; 10 per cent to 7,50,000; 15 per cent to 10,00,000; 20 per cent to 12,50,000; 25 per cent to 15,00,000; 30 per cent above; S62 and S64 confirm 2021-22 and 2022-23</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Financial years 2020-21, 2021-22 and 2022-23. An optional regime in these years.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -758,6 +1496,41 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[{"upto": "300000", "rate": "0"}, {"upto": "600000", "rate": "0.05"}, {"upto": "900000", "rate": "0.10"}, {"upto": "1200000", "rate": "0.15"}, {"upto": "1500000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S64 Finance Bill 2023 memorandum, section 115BAC(1A): Upto Rs. 3,00,000 Nil; 5 per cent to 6,00,000; 10 per cent to 9,00,000; 15 per cent to 12,00,000; 20 per cent to 15,00,000; 30 per cent above</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Financial year 2023-24: the new regime becomes the default.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -765,6 +1538,41 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[{"upto": "300000", "rate": "0"}, {"upto": "700000", "rate": "0.05"}, {"upto": "1000000", "rate": "0.10"}, {"upto": "1200000", "rate": "0.15"}, {"upto": "1500000", "rate": "0.20"}, {"upto": "", "rate": "0.30"}]</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S47 Finance (No.2) Bill 2024 memorandum: Upto Rs. 3,00,000 Nil; 5 per cent to 7,00,000; 10 per cent to 10,00,000; 15 per cent to 12,00,000; 20 per cent to 15,00,000; 30 per cent above; S65 confirms</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Financial year 2024-25.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -777,16 +1585,20 @@
           <t>[{"upto": "400000", "rate": "0"}, {"upto": "800000", "rate": "0.05"}, {"upto": "1200000", "rate": "0.10"}, {"upto": "1600000", "rate": "0.15"}, {"upto": "2000000", "rate": "0.20"}, {"upto": "2400000", "rate": "0.25"}, {"upto": "", "rate": "0.30"}]</t>
         </is>
       </c>
-      <c r="C10" s="2">
-        <v>45748</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>S65 Finance Bill 2025 memorandum: Upto Rs. 4,00,000 Nil; 5 per cent to 8,00,000; 10 per cent to 12,00,000; 15 per cent to 16,00,000; 20 per cent to 20,00,000; 25 per cent to 24,00,000; 30 per cent above; S55 Finance Bill 2026 memorandum: the same for tax year 2026-27 (section 202)</t>
         </is>
       </c>
-      <c r="F10" s="2">
-        <v>46295</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -810,52 +1622,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>regime</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiers</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>cap_special</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>cap_sections</t>
         </is>
@@ -867,6 +1679,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2013-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S56, S57 and S40 memoranda: No surcharge shall be levied in the cases of persons covered under paragraph A (individuals)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Financial years 2010-11 to 2012-13.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -874,6 +1721,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[{"above": "10000000", "rate": "0.10"}]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S19 Finance Bill 2013 memorandum: surcharge at ten per cent above Rs 1 crore; S41 the 2014 Bill: ten per cent</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Financial years 2013-14 and 2014-15.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -881,6 +1763,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>[{"above": "10000000", "rate": "0.12"}]</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S58 Finance Bill 2015 memorandum: surcharge at twelve percent above Rs 1 crore</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Financial year 2015-16.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -888,6 +1805,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[{"above": "10000000", "rate": "0.15"}]</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S59 Finance Bill 2016 memorandum: surcharge at fifteen percent above Rs 1 crore</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Financial year 2016-17.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -895,6 +1847,41 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S44 Finance Bill 2017 memorandum: ten per cent for total income above Rs 50 lakh up to Rs 1 crore, fifteen per cent above; S43 the 2018 Bill keeps it</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Financial years 2017-18 and 2018-19.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -902,6 +1889,51 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["111A", "112A"]}, {"above": "50000000", "rate": "0.37", "test_excludes": ["111A", "112A"]}]</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S61 Finance (No.2) Bill 2019 memorandum: 10%, 15%, 25% and 37% tiers; S66 the enhanced surcharge does not apply to sections 111A and 112A gains; S45 Finance Bill 2020 memorandum, Part I clause (a): (iii) and (iv) 'having a total income (excluding the income under the provisions of section 111A and 112A of the Act)', and the surcharge on the tax on that part is not above 15%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Financial year 2019-20. Dividends of mutual funds were exempt and company dividends above Rs 10 lakh taxed under 115BBDA, so no dividend is left out or capped here.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>["111A", "112A"]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -909,6 +1941,51 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["dividend", "111A", "112A"]}, {"above": "50000000", "rate": "0.37", "test_excludes": ["dividend", "111A", "112A"]}]</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S62 Finance Bill 2021 memorandum, clause (a) (i) to (v): (iii) and (iv) 'having a total income (excluding the income by way of dividend or income under the provisions of section 111A and 112A of the Act)', and the proviso: on income by way of dividend or under 111A and 112A the surcharge is not above 15%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Financial years 2020-21 and 2021-22. Section 112 gains are in the test and their tax is not capped.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>["dividend", "111A", "112A"]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -916,6 +1993,46 @@
           <t>old</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["dividend", "111A", "112", "112A", "196 (2025 Act)", "197 (2025 Act)", "198 (2025 Act)"]}, {"above": "50000000", "rate": "0.37", "test_excludes": ["dividend", "111A", "112", "112A", "196 (2025 Act)", "197 (2025 Act)", "198 (2025 Act)"]}]</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S63 Finance Bill 2022 memorandum, surcharge at source and on advance tax: (iii) and (iv) 'excluding the income by way of dividend or income under the provisions of sections 111A, 112 and 112A', proviso: not above 15% on that part; S64, S47, S65 and S55 memoranda repeat the tiers and the cap for 2023-24 to 2026-27</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Financial year 2022-23 onward; for 2026-27 the sections are 196, 197 and 198 of the Income-tax Act 2025 (S55), named here beside the old ones.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>["dividend", "111A", "112", "112A", "196 (2025 Act)", "197 (2025 Act)", "198 (2025 Act)"]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -923,6 +2040,51 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["dividend", "111A", "112A"]}, {"above": "50000000", "rate": "0.37", "test_excludes": ["dividend", "111A", "112A"]}]</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S45 and S62 memoranda: income-tax computed under section 115BAC is increased by the same surcharge tiers, with the 15% cap on dividend and section 111A and 112A tax</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Financial years 2020-21 and 2021-22.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>["dividend", "111A", "112A"]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -930,6 +2092,51 @@
           <t>new</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["dividend", "111A", "112", "112A"]}, {"above": "50000000", "rate": "0.37", "test_excludes": ["dividend", "111A", "112", "112A"]}]</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S63 Finance Bill 2022 memorandum: the same tiers under section 115BAC; the cap and the test now cover section 112 too</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Financial year 2022-23.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>["dividend", "111A", "112", "112A"]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -942,16 +2149,20 @@
           <t>[{"above": "5000000", "rate": "0.10"}, {"above": "10000000", "rate": "0.15"}, {"above": "20000000", "rate": "0.25", "test_excludes": ["dividend", "111A", "112", "112A", "196 (2025 Act)", "197 (2025 Act)", "198 (2025 Act)"]}]</t>
         </is>
       </c>
-      <c r="C12" s="2">
-        <v>45017</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>S64 Finance Bill 2023 memorandum: under section 115BAC(1A) 10% (Rs 50 lakh to Rs 1 crore), 15% (Rs 1 crore to Rs 2 crore), 25% above Rs 2 crore on income excluding dividend and gains at special rates, else 15%; the tax on such income is capped at 15%; S47, S65 and S55 repeat it</t>
         </is>
       </c>
-      <c r="F12" s="2">
-        <v>46295</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -985,42 +2196,42 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>asset_class</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>bucket</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
@@ -1032,6 +2243,36 @@
           <t>etf_equity</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S43 section 112A and S46 section 111A apply to STT-paid units of an equity oriented fund, whatever the date of purchase</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Equity oriented funds: at least 65% of the money in listed Indian equity shares (S43). Equity ETFs and arbitrage funds qualify.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1039,6 +2280,36 @@
           <t>mf_equity</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S43 section 112A and S46 section 111A apply to STT-paid units of an equity oriented fund, whatever the date of purchase</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Equity oriented funds: at least 65% of the money in listed Indian equity shares (S43). Equity ETFs and arbitrage funds qualify.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1046,6 +2317,41 @@
           <t>etf_gold</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S41 a unit of a mutual fund other than an equity oriented fund; S47 gold ETFs are outside section 50AA for units bought before 2023-04-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Gold ETF units bought before 2023-04-01 always keep the older rules (S46: section 50AA covers units acquired on or after 2023-04-01).</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1053,6 +2359,36 @@
           <t>etf_gold</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>gold_post_apr2023</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S46 clause 21: section 50AA covers a unit of a Specified Mutual Fund acquired on or after 2023-04-01; S47 the 35% equity test caught ETFs and gold ETFs; S49 lists gold ETFs</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Whether section 50AA bites depends on the SALE date (the definition of Specified Mutual Fund changed for sales from 2025-04-01): see tax.capital_gains.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1060,6 +2396,41 @@
           <t>mf_debt</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>debt_pre_apr2023</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>S41 a unit of a mutual fund other than an equity oriented fund; S46 clause 21: section 50AA covers only units acquired on or after 2023-04-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Debt and liquid fund units bought before 2023-04-01 keep the older rules, including indexation while it lasted.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1067,6 +2438,36 @@
           <t>mf_debt</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>debt_post_apr2023</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S46 clause 21: unit of a Specified Mutual Fund acquired on or after 2023-04-01; S49 debt, liquid, money market and gilt funds are Specified Mutual Funds</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gains are deemed short-term whatever the holding period.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1079,16 +2480,20 @@
           <t>equity</t>
         </is>
       </c>
-      <c r="C8" s="2">
-        <v>40269</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>S43 section 112A and S46 section 111A apply to STT-paid listed equity shares, whatever the date of purchase</t>
         </is>
       </c>
-      <c r="E8" s="2">
-        <v>46297</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,107 +2517,107 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>bucket</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>lt_months</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>st_treatment</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>st_rate</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>st_section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>lt_treatment</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>lt_section</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>lt_rate</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>indexation</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>lt_exemption_group</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>grandfather_acq_upto</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>lt_alt_rate</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>lt_alt_indexation</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>lt_alt_section</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>always_short</t>
         </is>
@@ -1224,6 +2629,64 @@
           <t>equity</t>
         </is>
       </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>111A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>exempt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>10(38)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>S40 section 111A tax on short-term gains is 15%; S43 long-term gains on STT-paid equity and equity oriented fund units are exempt under section 10(38) until withdrawn from 2018-04-01; S41 same benefits: long-term exempt, short-term 15%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>The rule covers STT-paid sales, which is every sale in the modelled universe (exchange sales and redemptions of equity funds). A long-term loss here is not allowed against other gains because the gain would have been exempt.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1231,6 +2694,82 @@
           <t>equity</t>
         </is>
       </c>
+      <c r="B3">
+        <v>12</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>111A</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>112A</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>S43 section 112A: 10% on long-term gains above Rs 1 lakh, no indexation, cost grandfathered to the value on 31 Jan 2018; S46 First Schedule: section 111A 15% and section 112A 10% for transfers before 2024-07-23</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Holding period 12 months. The Rs 1 lakh yearly exemption is in tax.lt_exemption (group equity_112a). For units bought on or before 2018-01-31 the value on 31 Jan 2018 is needed (highest quoted price for listed units, NAV for unlisted units).</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="O3" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>equity_112a</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2018-01-31</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1238,6 +2777,82 @@
           <t>equity</t>
         </is>
       </c>
+      <c r="B4">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>111A</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>112A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>S46 First Schedule: section 111A 20% and section 112A 12.5% for transfers on or after 2024-07-23; S48 the new provisions apply to any transfer on or after 2024-07-23, exemption limit Rs 1.25 lakh</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Holding period stays 12 months for listed securities and equity oriented fund units (S46 clause 3). Grandfathering to 31 Jan 2018 continues.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>equity_112a</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2018-01-31</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1245,6 +2860,77 @@
           <t>equity</t>
         </is>
       </c>
+      <c r="B5">
+        <v>12</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>196 (2025 Act)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>198 (2025 Act)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>S55 Income-tax Act 2025 section 196: short-term gains on STT-paid equity 20%; section 198: long-term gains above Rs 1,25,000 at 12.5%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sale date on or after 2026-04-01 falls under the Income-tax Act 2025. Rates and the exemption limit are from sections 196 to 198 (S55). The 12 and 24 month holding periods are as the Act 2025 defines them (section 2(101), read in secondary summaries only); the 31 Jan 2018 grandfathering and the section 50AA carry-over were not checked against the Act text and are taken as unchanged.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>equity_112a</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2018-01-31</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1252,6 +2938,80 @@
           <t>gold</t>
         </is>
       </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2014-07-10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>S41 existing law: a mutual fund unit is long-term after 12 months and the section 112 proviso lets units use 10% without indexation; S42 paras 5.2 and 30.2: the older rules stay for transfers up to 2014-07-10; S47 long-term gains were 20% with indexation under section 112</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Tax is the lower of 20% on the indexed gain and 10% on the gain without indexation (lt_alt_*). Indexation uses the old-base index (tax.cii series 1981).</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>112 (10% option)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1259,6 +3019,67 @@
           <t>gold</t>
         </is>
       </c>
+      <c r="B7">
+        <v>36</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>S42 paras 5.2 and 30.2: a unit of a mutual fund other than an equity oriented fund is long-term after 36 months and the 10% option is gone, for transfers from 2014-07-11; S47 20% with indexation under section 112</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Indexation uses the old-base index for sales up to 2017-03-31 and the 2001-base index after that (tax.cii).</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1266,6 +3087,67 @@
           <t>gold</t>
         </is>
       </c>
+      <c r="B8">
+        <v>12</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>S46 clause 3: section 2(42A) now says 12 months for a security listed on a recognised stock exchange, with the words (other than a unit) removed; S49 listed units 12 months from 2024-07-23</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Rate 12.5% without indexation for all long-term gains under section 112 (S46, S48). A listed unit (gold ETF) is long-term after 12 months from 2024-07-23 (the words other than a unit were dropped from the listed-securities rule).</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1273,6 +3155,62 @@
           <t>gold</t>
         </is>
       </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>197 (2025 Act)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>S55 Income-tax Act 2025 section 197: long-term gains 12.5%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Sale date on or after 2026-04-01 falls under the Income-tax Act 2025. Rates and the exemption limit are from sections 196 to 198 (S55). The 12 and 24 month holding periods are as the Act 2025 defines them (section 2(101), read in secondary summaries only); the 31 Jan 2018 grandfathering and the section 50AA carry-over were not checked against the Act text and are taken as unchanged.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1280,6 +3218,80 @@
           <t>debt_pre_apr2023</t>
         </is>
       </c>
+      <c r="B10">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2014-07-10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>S41 existing law: a mutual fund unit is long-term after 12 months and the section 112 proviso lets units use 10% without indexation; S42 paras 5.2 and 30.2: the older rules stay for transfers up to 2014-07-10; S47 long-term gains were 20% with indexation under section 112</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Tax is the lower of 20% on the indexed gain and 10% on the gain without indexation (lt_alt_*). Indexation uses the old-base index (tax.cii series 1981).</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>112 (10% option)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1287,6 +3299,67 @@
           <t>debt_pre_apr2023</t>
         </is>
       </c>
+      <c r="B11">
+        <v>36</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2014-07-11</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2024-07-22</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>S42 paras 5.2 and 30.2: a unit of a mutual fund other than an equity oriented fund is long-term after 36 months and the 10% option is gone, for transfers from 2014-07-11; S47 20% with indexation under section 112</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Indexation uses the old-base index for sales up to 2017-03-31 and the 2001-base index after that (tax.cii).</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1294,6 +3367,67 @@
           <t>debt_pre_apr2023</t>
         </is>
       </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>S46 clause 3 and S48: 24 months for assets other than listed securities; S49 unlisted units 24 months from 2024-07-23</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Rate 12.5% without indexation for all long-term gains under section 112 (S46, S48). An unlisted unit (debt or liquid fund) is long-term after 24 months from 2024-07-23.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1301,6 +3435,62 @@
           <t>debt_pre_apr2023</t>
         </is>
       </c>
+      <c r="B13">
+        <v>24</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>197 (2025 Act)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>S55 Income-tax Act 2025 section 197: long-term gains 12.5%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Sale date on or after 2026-04-01 falls under the Income-tax Act 2025. Rates and the exemption limit are from sections 196 to 198 (S55). The 12 and 24 month holding periods are as the Act 2025 defines them (section 2(101), read in secondary summaries only); the 31 Jan 2018 grandfathering and the section 50AA carry-over were not checked against the Act text and are taken as unchanged.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1308,6 +3498,49 @@
           <t>gold_post_apr2023</t>
         </is>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>50AA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>S46 clause 21: section 50AA deems the gain on a unit of a Specified Mutual Fund acquired on or after 2023-04-01 to be short-term; S47 the not-more-than-35%-in-equity test covered gold ETFs; S49 gold ETFs are Specified Mutual Funds for FY 2024-25</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Taxed at slab rates whatever the holding period; no indexation. Ends for sales from 2025-04-01 when the definition changes (S47).</t>
+        </is>
+      </c>
+      <c r="U14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1315,6 +3548,67 @@
           <t>gold_post_apr2023</t>
         </is>
       </c>
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>S46 clause 21(b): new Specified Mutual Fund definition (more than 65% in debt and money market instruments) from 2026-04-01, i.e. AY 2026-27; S47 the new definition applies from AY 2026-27; S49 from FY 2025-26 only debt-oriented schemes are covered</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>A gold ETF is no longer a Specified Mutual Fund for sales from 2025-04-01, so the ordinary rules apply: 12 months (listed unit), 12.5% without indexation.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1322,6 +3616,62 @@
           <t>gold_post_apr2023</t>
         </is>
       </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>normal rates</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>special</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>197 (2025 Act)</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>S55 Income-tax Act 2025 section 197: long-term gains 12.5%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Sale date on or after 2026-04-01 falls under the Income-tax Act 2025. Rates and the exemption limit are from sections 196 to 198 (S55). The 12 and 24 month holding periods are as the Act 2025 defines them (section 2(101), read in secondary summaries only); the 31 Jan 2018 grandfathering and the section 50AA carry-over were not checked against the Act text and are taken as unchanged.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.125</t>
+        </is>
+      </c>
+      <c r="O16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1329,6 +3679,49 @@
           <t>debt_post_apr2023</t>
         </is>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50AA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>S46 clause 21 and S47: section 50AA deems gains on units of a Specified Mutual Fund acquired on or after 2023-04-01 short-term; S49 debt, liquid, money market and gilt funds are Specified Mutual Funds in FY 2024-25 and after the 2025-26 change</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Taxed at slab rates whatever the holding period; no indexation.</t>
+        </is>
+      </c>
+      <c r="U17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1346,16 +3739,20 @@
           <t>50AA equivalent (2025 Act)</t>
         </is>
       </c>
-      <c r="H18" s="2">
-        <v>46113</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>S49 debt-oriented funds stay Specified Mutual Funds; S55 the Income-tax Act 2025 rewrites the 1961 sections</t>
         </is>
       </c>
-      <c r="K18" s="2">
-        <v>46295</v>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1382,37 +3779,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1424,6 +3821,36 @@
           <t>0.03</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S57 Finance Bill 2011 memorandum: Education Cess two per cent and Secondary and Higher Education Cess one per cent on the tax including surcharge; S44 says the same for 2017-18</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Two cesses (2% and 1%) add up to 3%.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1431,16 +3858,20 @@
           <t>0.04</t>
         </is>
       </c>
-      <c r="B3" s="2">
-        <v>43191</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>S43 Finance Bill 2018 memorandum: the two cesses are discontinued and a Health and Education Cess of four per cent is levied; S61, S64, S65 and S55 repeat 4% in later years</t>
         </is>
       </c>
-      <c r="E3" s="2">
-        <v>46295</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1459,42 +3890,42 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>series</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1506,6 +3937,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2011-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S50 notification No. 59/2010 of 2010-07-21: 2010-11 = 711</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1513,6 +3979,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>785</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2012-03-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S50 notification No. 35/2011 of 2011-06-23: 2011-12 = 785</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1520,6 +4021,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2013-03-31</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S50 notification No. 38/2012 of 2012-09-17: 2012-13 = 852</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1527,6 +4063,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S50 notification No. 40/2013 of 2013-06-06: 2013-14 = 939</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1534,6 +4105,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>S50 notification No. 31/2014 of 2014-06-11: 2014-15 = 1024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1541,6 +4147,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>S50 notification No. 60/2015 of 2015-07-24: 2015-16 = 1081</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1548,6 +4189,41 @@
           <t>1981</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>S50 notification No. 42/2016 of 2016-06-02: 2016-17 = 1125</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Old base. Used for sales up to 2017-03-31 (S44). Value confirmed by the TaxGuru table; the notification itself was read only as a news report.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1555,6 +4231,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2011-03-31</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2010-11 = 167</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1562,6 +4268,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2011-04-01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2012-03-31</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2011-12 = 184</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1569,6 +4305,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2012-04-01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2013-03-31</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2012-13 = 200</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1576,6 +4342,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2013-14 = 220</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1583,6 +4379,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2014-04-01</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2015-03-31</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2014-15 = 240</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1590,6 +4416,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2015-16 = 254</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1597,6 +4453,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2017-03-31</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2016-17 = 264</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1604,6 +4490,41 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2017-04-01</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2017-18 = 272</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>First year whose sales use the new base (S44).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,6 +4532,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2019-03-31</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2018-19 = 280</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1618,6 +4569,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2019-20 = 289</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1625,6 +4606,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2021-03-31</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S51 table 2001-02 = 100: 2020-21 = 301</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1632,6 +4643,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2021-04-01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2022-03-31</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>S52 table 2001-02 = 100: 2021-22 = 317</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1639,6 +4680,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>S52 table 2001-02 = 100: 2022-23 = 331</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1646,6 +4717,36 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>S52 table 2001-02 = 100: 2023-24 = 348</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1653,6 +4754,41 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>S52 table 2001-02 = 100: 2024-25 = 363</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Indexation is not allowed for sales on or after 2024-07-23 (S46); sales from 2024-04-01 to 2024-07-22 still use this value.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1660,6 +4796,41 @@
           <t>2001</t>
         </is>
       </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>S52 table 2001-02 = 100: 2025-26 = 376</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>secondary</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Not used for any class modelled here: indexation ended for sales on or after 2024-07-23 (S46). Kept so the series is complete.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1672,16 +4843,20 @@
           <t>384</t>
         </is>
       </c>
-      <c r="C25" s="2">
-        <v>46113</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>S53 CBDT notified 384 for 2026-27</t>
         </is>
       </c>
-      <c r="F25" s="2">
-        <v>46295</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1705,37 +4880,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1747,6 +4922,36 @@
           <t>tax_round_step</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S67 section 288B: tax payable is rounded to the nearest multiple of ten rupees, paise ignored, five or more rounds up</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Total income is also rounded to the nearest Rs 10 (section 288A); that is not modelled (it moves tax by at most Rs 1.5).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1754,6 +4959,36 @@
           <t>setoff_order</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>as coded in engine/tax.py</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>S0 the law fixes only that a short-term loss may be set off against any capital gain and a long-term loss against long-term gains only (S54); S69 says brought-forward losses are set off before the section 112A exemption</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>As coded: this year's short-term loss on short-term gains, long-term loss on long-term gains, leftover short-term loss on long-term gains, then losses brought forward (long-term first, oldest first), highest special rate first, then slab-taxed gains; then the yearly exemption.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1761,6 +4996,36 @@
           <t>shortfall_order</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>as coded in engine/tax.py</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S0 the law says only that gains shrink by the unused basic exemption of a resident individual (S55 sections 196(2) and 198(3) of the Income-tax Act 2025, the same as the 1961 Act provisos); S69 says the highest-rate gain is usually taken first</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>As coded: a resident individual's unused basic exemption is applied to gains taxed at special rates, highest rate first, after the yearly section 112A exemption. S69 reports that the Income Tax portal calculator (June 2025) applied it to equity gains before the section 112A exemption when equity and other long-term gains are both taxed at 12.5%; this model takes the exemption first, which gives the lower tax.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1768,6 +5033,36 @@
           <t>business_loss_setoff</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>interest and slab-taxed income only, not the other income given, as coded in engine/tax.py</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S0 assumption: the law lets a loss under the head business be set off against income under any head except salary, capital gains included (S75 section 71(1), (2) and (2A)); this engine sets it off against interest and income taxed at slab rates only</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Conservative. Section 71(2A) bars setting a business loss off against salary, and the other taxable income a user gives may be salary, so it is never touched. A futures loss lowers interest, dividends at slab rates and gains at slab rates, and is never set off against gains taxed at special rates (the law would allow that). What is left over is carried forward for business income only (S75 section 72, S76 section 112). Cost if wrong: a user whose other income is not salary (rent, another business) gets the set-off a year later instead of at once; a user with special-rate gains in a loss year pays more tax that year than the law asks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1780,16 +5075,20 @@
           <t>the income above a surcharge threshold is taken from slab income first, then from gains at special rates, lowest rate first, as coded in engine/tax.py</t>
         </is>
       </c>
-      <c r="C6" s="2">
-        <v>40269</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>S0 assumption: the provisos on surcharge (see rules/tax/surcharge.toml, S61 and S62) limit tax and surcharge to the tax on the threshold income plus the income above it, without saying which income counts as the income above it</t>
         </is>
       </c>
-      <c r="E6" s="2">
-        <v>46295</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1813,52 +5112,52 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>payer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>threshold</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -1870,6 +5169,41 @@
           <t>company</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>exempt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2016-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>S59 Finance Bill 2016 memorandum: dividend which suffers distribution tax under section 115-O is exempt in the hands of the shareholder under section 10(34)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Exempt in full.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1877,6 +5211,51 @@
           <t>company</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>above_threshold</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2016-04-01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>S59 Finance Bill 2016 memorandum: dividend in excess of Rs 10 lakh chargeable at ten percent for a resident individual, HUF or firm from 1 April 2017 (AY 2017-18); S79 section 115BBDA(1): dividends declared, distributed or paid by a domestic company; S44 confirms; S45 it covers dividends up to 2020-03-31</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>The dividends up to Rs 10 lakh stay exempt. No deduction or set-off of loss is allowed against the taxed part (section 115BBDA(2)), and the unused basic exemption does not shelter it.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1884,6 +5263,36 @@
           <t>company</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>slab</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>S45 dividends and unit income received on or after 2020-04-01 are taxed at the holder's applicable rates</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Added to income at slab rates. Interest expense against it is capped at 20% of the dividend (S45); no such expense is modelled.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1891,6 +5300,41 @@
           <t>fund</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>exempt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2020-03-31</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>S45 Finance Bill 2020 memorandum: before 2020-04-01 dividend and unit income were exempt under sections 10(34) and 10(35) because the payer paid distribution tax; S79 section 115BBDA covers dividends of domestic companies only</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Income from units of mutual funds and ETFs stayed exempt through 2019-20 (section 10(35)); section 115BBDA never applied to it.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1903,16 +5347,20 @@
           <t>slab</t>
         </is>
       </c>
-      <c r="C6" s="2">
-        <v>43922</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2020-04-01</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>S45 dividends and unit income received on or after 2020-04-01 are taxed at the holder's applicable rates</t>
         </is>
       </c>
-      <c r="F6" s="2">
-        <v>46295</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1936,37 +5384,37 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>kind</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -1978,6 +5426,36 @@
           <t>capital</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S54 section 74(2): no capital loss is carried forward for more than eight assessment years; the e-Filing FAQ says the eight-year limit continues under the Income-tax Act 2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Short-term losses set off against any capital gain, long-term losses against long-term gains only.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1990,16 +5468,20 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C3" s="2">
-        <v>40269</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2010-04-01</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>S75 section 72(3): no loss shall be carried forward under this section for more than eight assessment years immediately succeeding the assessment year for which the loss was first computed; S76 section 112(2) of the Income-tax Act 2025 says the same for eight tax years</t>
         </is>
       </c>
-      <c r="E3" s="2">
-        <v>46295</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -2023,47 +5505,47 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>from</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>to</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>verified_on</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -2075,6 +5557,46 @@
           <t>equity_112a</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lowest_rate_first</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2018-04-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>S43 section 112A: 10% on long-term gains exceeding Rs 1 lakh</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>One rate in these years, so the order does not matter. Before 2018-04-01 the gains were exempt in full (tax.capital_gains).</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2082,6 +5604,46 @@
           <t>equity_112a</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>125000</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>lowest_rate_first</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>S46 clause 31 proviso: the limit of Rs 1.25 lakh applies on the aggregate of the gains before and after 2024-07-23; S48 the limit applies for FY 2024-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>assumed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>The amount is from the law. The ORDER is assumed: gains before 2024-07-23 (10%) and on or after it (12.5%) can both arise in this year and no source says which one the limit is used against first. The Act lists the 10% part first, and using it there is the less favourable choice for the taxpayer, so lowest_rate_first is used.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2099,16 +5661,20 @@
           <t>lowest_rate_first</t>
         </is>
       </c>
-      <c r="D4" s="2">
-        <v>45748</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>S48 the exemption limit of Rs 1.25 lakh applies for FY 2024-25 and later years; S55 section 198(2)(a): Rs 1,25,000</t>
         </is>
       </c>
-      <c r="G4" s="2">
-        <v>46295</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
